--- a/Tableau de synthese.xlsx
+++ b/Tableau de synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\userinsta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD169BC7-1EAD-44E3-BA46-00F43C6A012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D9DDCB-A18C-4CF3-A043-9835ECD38EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -124,10 +124,37 @@
     <t>NOM et prénom : KENAKA THIERRY</t>
   </si>
   <si>
-    <t xml:space="preserve">Adresse URL du portfolio : </t>
-  </si>
-  <si>
     <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://github.com/christkenaka-ops/tableausynthese</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X </t>
+  </si>
+  <si>
+    <t>POJET:Application Console, Développement d'une application console permettant la gestion d'opérations de base,Technologies utilisées:C#, .NET, Visual Studio Code</t>
+  </si>
+  <si>
+    <t>PROJET: Site e-commerce - Création d'une boutique en ligne avec gestion des produits et commandes.                                                                              Technologies utilisées: HTML, CSS, JavaScript, PHP, MySQL</t>
+  </si>
+  <si>
+    <t>PROJET: Multi-convertisseur - Application de conversion (devises, températures, longueurs, etc.).                                                                              Technologies utilisées: C#, .NET, Visual Studio Code</t>
+  </si>
+  <si>
+    <t>PROJET: Bibliobus - Système de gestion d'une bibliothèque mobile avec suivi des livres et emprunts.                                                                              Technologies utilisées: PHP, MySQL, HTML, CSS, JavaScript</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJET: Portfolio - Site web présentant le parcours, les compétences et les réalisations.                                                                             Technologies utilisées: HTML, CSS, JavaScript - </t>
+  </si>
+  <si>
+    <t>PROJET:Création d'un site pour un salon de coiffure,avec gestion de produit,Technologies utilisées: HTML, CSS, JavaScript, PHP, MySQL</t>
   </si>
 </sst>
 </file>
@@ -599,7 +626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -729,6 +756,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1058,7 +1088,7 @@
       <c r="E1" s="24"/>
       <c r="F1" s="24"/>
       <c r="G1" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H1" s="24"/>
     </row>
@@ -1111,7 +1141,7 @@
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
@@ -1252,14 +1282,26 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
+      <c r="E9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>29</v>
+      </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1297,14 +1339,26 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="44">
+        <v>46116</v>
+      </c>
       <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="D10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+      <c r="H10" s="16" t="s">
+        <v>29</v>
+      </c>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1342,14 +1396,24 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="44">
+        <v>46093</v>
+      </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="H11" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1387,14 +1451,24 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="44">
+        <v>46070</v>
+      </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
+      <c r="H12" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1432,14 +1506,26 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="44">
+        <v>46046</v>
+      </c>
       <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="D13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
+      <c r="H13" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1749,14 +1835,28 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="A20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="44">
+        <v>46152</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
